--- a/Data/Edit_Lead.xlsx
+++ b/Data/Edit_Lead.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bssuniversal-my.sharepoint.com/personal/amyma_usman_bssuniversal_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AmymaUsman\PycharmProjects\SmartCRM_Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{1B0D683B-57EE-495E-837C-B89679093348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{937AA65F-1375-4DDA-8F7D-B1AC52126210}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56B52AC-F3F6-408C-A6DB-7C49EDE642FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{39371DC4-D2EF-40A1-B941-B000820DCB7F}"/>
   </bookViews>
@@ -41,31 +41,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
-    <t>${TITLE_FIELD_TEXT}</t>
-  </si>
-  <si>
     <t>Ali Admin</t>
   </si>
   <si>
-    <t xml:space="preserve">${FIRSTNAME_FIELD_TEXT} </t>
-  </si>
-  <si>
     <t>Ali</t>
   </si>
   <si>
-    <t>${LASTNAME_FIELD_TEXT}</t>
-  </si>
-  <si>
     <t>Admin</t>
   </si>
   <si>
-    <t>${NAME_FIELD_TEXT}</t>
-  </si>
-  <si>
-    <t>${LINKDIN_TEXT}</t>
-  </si>
-  <si>
     <t>TestLead_717</t>
+  </si>
+  <si>
+    <t>${TITLE_FIELD_EDITED_TEXT}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${FIRSTNAME_FIELD_EDITED_TEXT} </t>
+  </si>
+  <si>
+    <t>${LASTNAME_FIELD_EDITED_TEXT}</t>
+  </si>
+  <si>
+    <t>${NAME_FIELD_EDITED_TEXT}</t>
+  </si>
+  <si>
+    <t>${LINKDIN_EDITED_TEXT}</t>
   </si>
 </sst>
 </file>
@@ -449,36 +449,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
